--- a/demo/configs/ItemConfig.xlsx
+++ b/demo/configs/ItemConfig.xlsx
@@ -40,7 +40,7 @@
     <t>1001</t>
   </si>
   <si>
-    <t>信用点</t>
+    <t>摩拉</t>
   </si>
   <si>
     <t>currency</t>
@@ -61,88 +61,88 @@
     <t>1002</t>
   </si>
   <si>
-    <t>星琼</t>
+    <t>原石</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>稀有货币（演示）</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>冒险阅历</t>
+  </si>
+  <si>
+    <t>exp</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>冒险等级经验（演示）</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>大英雄的经验</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>9999</t>
+  </si>
+  <si>
+    <t>角色经验书（演示）</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>武器突破矿石</t>
+  </si>
+  <si>
+    <t>999</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>武器培养材料（演示）</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>相遇之缘</t>
+  </si>
+  <si>
+    <t>gacha_ticket</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>稀有货币（演示）</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>角色经验</t>
-  </si>
-  <si>
-    <t>exp</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>升级材料</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>漫游指南</t>
-  </si>
-  <si>
-    <t>material</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>999</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>行迹材料（演示）</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>遗器残骸</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>装备材料（演示）</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>星轨专票</t>
-  </si>
-  <si>
-    <t>gacha_ticket</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>抽卡券（演示）</t>
+    <t>常驻祈愿券（演示）</t>
   </si>
   <si>
     <t>4001</t>
   </si>
   <si>
-    <t>开拓者碎片</t>
+    <t>命星·演示</t>
   </si>
   <si>
     <t>hero_shard</t>
   </si>
   <si>
-    <t>英雄碎片（演示）</t>
+    <t>角色命星（演示）</t>
   </si>
   <si>
     <t>5001</t>
@@ -573,18 +573,18 @@
         <v>27</v>
       </c>
       <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
         <v>28</v>
-      </c>
-      <c r="G5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
         <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -593,7 +593,7 @@
         <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
         <v>32</v>
@@ -616,7 +616,7 @@
         <v>37</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -639,7 +639,7 @@
         <v>16</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
